--- a/docs/test-design/测试用例模板.xlsx
+++ b/docs/test-design/测试用例模板.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w26148\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\code\test_case_gen\docs\test-design\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94365E62-0E5F-466F-A606-4B9FB024E6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11970" windowHeight="2070"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -38,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -52,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -66,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -80,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -94,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -122,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -150,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -178,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -192,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -206,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -220,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -248,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -262,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -276,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -290,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -304,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -318,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -332,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -346,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -362,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -464,7 +465,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -543,12 +544,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -837,104 +837,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="8" style="1"/>
-    <col min="14" max="14" width="8" style="2"/>
+    <col min="14" max="14" width="8" style="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="45.75" customWidth="1"/>
+    <col min="17" max="17" width="48.625" customWidth="1"/>
+    <col min="18" max="18" width="13.375" customWidth="1"/>
+    <col min="19" max="19" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="56.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="R2:R2001">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R2001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"功能测试,性能规格测试,可靠性测试,兼容性测试,可维护性测试,安全性测试,易用性测试"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S2:S2001">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S2001" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"L1,L2,L3,L4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T2001">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T2001" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"自动化,手动"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/test-design/测试用例模板.xlsx
+++ b/docs/test-design/测试用例模板.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w26148\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\code\test_case_gen\docs\test-design\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A7D5B9-CC42-4245-920A-F81B3B4A3027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11970" windowHeight="2070"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -38,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -52,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -66,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -80,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -94,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -122,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -150,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -178,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -192,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -206,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -220,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -248,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -262,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -276,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -290,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -304,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -318,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -332,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -346,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -362,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -464,7 +465,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -543,12 +544,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -837,104 +837,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="8" style="1"/>
-    <col min="14" max="14" width="8" style="2"/>
+    <col min="14" max="14" width="8" style="1"/>
+    <col min="15" max="15" width="40.875" customWidth="1"/>
+    <col min="16" max="16" width="59.125" customWidth="1"/>
+    <col min="17" max="17" width="52.125" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="20" max="20" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="56.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="R2:R2001">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R2001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"功能测试,性能规格测试,可靠性测试,兼容性测试,可维护性测试,安全性测试,易用性测试"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S2:S2001">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S2001" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"L1,L2,L3,L4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T2001">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T2001" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"自动化,手动"</formula1>
     </dataValidation>
   </dataValidations>
